--- a/ch_04/ch_04_solution.xlsx
+++ b/ch_04/ch_04_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30515"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_04_eda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_04\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8603F6F-2B34-4614-9750-0CD8BBE86C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="14586" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1985,19 +1985,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K399"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.1171875" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12.41015625" customWidth="1"/>
-    <col min="5" max="5" width="8.1171875" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" customWidth="1"/>
+    <col min="5" max="5" width="8.1328125" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12.17578125" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>18</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>15</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>18</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>16</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>17</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>15</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>14</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>14</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>15</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>15</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>14</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>15</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>24</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>22</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>18</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>21</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>27</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>26</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>25</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>24</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>25</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>26</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>21</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>10</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>10</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>11</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>9</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>25</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>25</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>19</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>16</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>17</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>19</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>18</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>14</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>14</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>14</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>14</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>12</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>13</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>13</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>18</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>22</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>19</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>18</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>23</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>28</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>30</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>30</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>31</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>35</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>27</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>26</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>24</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>25</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>23</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>20</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>21</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>13</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>14</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>15</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>14</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>17</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>11</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>13</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>12</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>13</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>19</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>15</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>13</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>13</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>14</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>18</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>22</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>21</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>26</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>22</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>28</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>23</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>28</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>27</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>13</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>14</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>13</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>14</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>15</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>12</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>13</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>13</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>14</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>13</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>12</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>13</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>18</v>
       </c>
@@ -4869,7 +4869,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>16</v>
       </c>
@@ -4898,7 +4898,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>18</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>18</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>23</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>26</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>11</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>12</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>13</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>12</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>18</v>
       </c>
@@ -5159,7 +5159,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>20</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>21</v>
       </c>
@@ -5217,7 +5217,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>22</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>18</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>19</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>21</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>26</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>15</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>16</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>29</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>24</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>20</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>19</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>15</v>
       </c>
@@ -5565,7 +5565,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>24</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>20</v>
       </c>
@@ -5623,7 +5623,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>11</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>20</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>21</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>19</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>15</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>31</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>26</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>32</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>25</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>16</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>16</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>18</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>16</v>
       </c>
@@ -5997,7 +5997,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>13</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>14</v>
       </c>
@@ -6055,7 +6055,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>14</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>14</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>29</v>
       </c>
@@ -6142,7 +6142,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>26</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>26</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>31</v>
       </c>
@@ -6229,7 +6229,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>32</v>
       </c>
@@ -6258,7 +6258,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>28</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>24</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>26</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>24</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>26</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>31</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>19</v>
       </c>
@@ -6461,7 +6461,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>18</v>
       </c>
@@ -6490,7 +6490,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>15</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>15</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>16</v>
       </c>
@@ -6577,7 +6577,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>15</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>16</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>14</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>17</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>16</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>15</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>18</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>21</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>20</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>13</v>
       </c>
@@ -6867,7 +6867,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>29</v>
       </c>
@@ -6896,7 +6896,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>23</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>20</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>23</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>24</v>
       </c>
@@ -7012,7 +7012,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>25</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>24</v>
       </c>
@@ -7070,7 +7070,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>18</v>
       </c>
@@ -7099,7 +7099,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>29</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>19</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>23</v>
       </c>
@@ -7186,7 +7186,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>23</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>22</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>25</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>33</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>28</v>
       </c>
@@ -7331,7 +7331,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>25</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>25</v>
       </c>
@@ -7389,7 +7389,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>26</v>
       </c>
@@ -7418,7 +7418,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>27</v>
       </c>
@@ -7447,7 +7447,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>17.5</v>
       </c>
@@ -7476,7 +7476,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>16</v>
       </c>
@@ -7505,7 +7505,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>15.5</v>
       </c>
@@ -7534,7 +7534,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>14.5</v>
       </c>
@@ -7563,7 +7563,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>22</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>22</v>
       </c>
@@ -7621,7 +7621,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>24</v>
       </c>
@@ -7650,7 +7650,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>22.5</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>29</v>
       </c>
@@ -7708,7 +7708,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>24.5</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>29</v>
       </c>
@@ -7766,7 +7766,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>33</v>
       </c>
@@ -7795,7 +7795,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>20</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>18</v>
       </c>
@@ -7853,7 +7853,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>18.5</v>
       </c>
@@ -7882,7 +7882,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>17.5</v>
       </c>
@@ -7911,7 +7911,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>29.5</v>
       </c>
@@ -7940,7 +7940,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>32</v>
       </c>
@@ -7969,7 +7969,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>28</v>
       </c>
@@ -7998,7 +7998,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>26.5</v>
       </c>
@@ -8027,7 +8027,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>20</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>13</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>19</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>19</v>
       </c>
@@ -8143,7 +8143,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>16.5</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>16.5</v>
       </c>
@@ -8201,7 +8201,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>13</v>
       </c>
@@ -8230,7 +8230,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>13</v>
       </c>
@@ -8259,7 +8259,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>13</v>
       </c>
@@ -8288,7 +8288,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>31.5</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>30</v>
       </c>
@@ -8346,7 +8346,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>36</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>25.5</v>
       </c>
@@ -8404,7 +8404,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>33.5</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>17.5</v>
       </c>
@@ -8462,7 +8462,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>17</v>
       </c>
@@ -8491,7 +8491,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>15.5</v>
       </c>
@@ -8520,7 +8520,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>15</v>
       </c>
@@ -8549,7 +8549,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>17.5</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>20.5</v>
       </c>
@@ -8607,7 +8607,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>19</v>
       </c>
@@ -8636,7 +8636,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>18.5</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>16</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>15.5</v>
       </c>
@@ -8723,7 +8723,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>15.5</v>
       </c>
@@ -8752,7 +8752,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>16</v>
       </c>
@@ -8781,7 +8781,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>29</v>
       </c>
@@ -8810,7 +8810,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>24.5</v>
       </c>
@@ -8839,7 +8839,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>26</v>
       </c>
@@ -8868,7 +8868,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>25.5</v>
       </c>
@@ -8897,7 +8897,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>30.5</v>
       </c>
@@ -8926,7 +8926,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>33.5</v>
       </c>
@@ -8955,7 +8955,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>30</v>
       </c>
@@ -8984,7 +8984,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>30.5</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>22</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>21.5</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>21.5</v>
       </c>
@@ -9100,7 +9100,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>43.1</v>
       </c>
@@ -9129,7 +9129,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>36.1</v>
       </c>
@@ -9158,7 +9158,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>32.799999999999997</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>39.4</v>
       </c>
@@ -9216,7 +9216,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>36.1</v>
       </c>
@@ -9245,7 +9245,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>19.899999999999999</v>
       </c>
@@ -9274,7 +9274,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>19.399999999999999</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>20.2</v>
       </c>
@@ -9332,7 +9332,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>19.2</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>20.5</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>20.2</v>
       </c>
@@ -9419,7 +9419,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>25.1</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>20.5</v>
       </c>
@@ -9477,7 +9477,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>19.399999999999999</v>
       </c>
@@ -9506,7 +9506,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>20.6</v>
       </c>
@@ -9535,7 +9535,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>20.8</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>18.600000000000001</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>18.100000000000001</v>
       </c>
@@ -9622,7 +9622,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>19.2</v>
       </c>
@@ -9651,7 +9651,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>17.7</v>
       </c>
@@ -9680,7 +9680,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>18.100000000000001</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>17.5</v>
       </c>
@@ -9738,7 +9738,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>30</v>
       </c>
@@ -9767,7 +9767,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>27.5</v>
       </c>
@@ -9796,7 +9796,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>27.2</v>
       </c>
@@ -9825,7 +9825,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>30.9</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>21.1</v>
       </c>
@@ -9883,7 +9883,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>23.2</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>23.8</v>
       </c>
@@ -9941,7 +9941,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>23.9</v>
       </c>
@@ -9970,7 +9970,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>20.3</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>17</v>
       </c>
@@ -10028,7 +10028,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>21.6</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>16.2</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>31.5</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>29.5</v>
       </c>
@@ -10144,7 +10144,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>21.5</v>
       </c>
@@ -10173,7 +10173,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>19.8</v>
       </c>
@@ -10202,7 +10202,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>22.3</v>
       </c>
@@ -10231,7 +10231,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>20.2</v>
       </c>
@@ -10260,7 +10260,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>20.6</v>
       </c>
@@ -10289,7 +10289,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>17</v>
       </c>
@@ -10318,7 +10318,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>17.600000000000001</v>
       </c>
@@ -10347,7 +10347,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>16.5</v>
       </c>
@@ -10376,7 +10376,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>18.2</v>
       </c>
@@ -10405,7 +10405,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>16.899999999999999</v>
       </c>
@@ -10434,7 +10434,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>15.5</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>19.2</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>18.5</v>
       </c>
@@ -10521,7 +10521,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>31.9</v>
       </c>
@@ -10550,7 +10550,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>34.1</v>
       </c>
@@ -10579,7 +10579,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>35.700000000000003</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>27.4</v>
       </c>
@@ -10637,7 +10637,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>25.4</v>
       </c>
@@ -10666,7 +10666,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>23</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>27.2</v>
       </c>
@@ -10724,7 +10724,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>23.9</v>
       </c>
@@ -10753,7 +10753,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>34.200000000000003</v>
       </c>
@@ -10782,7 +10782,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>34.5</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>31.8</v>
       </c>
@@ -10840,7 +10840,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>37.299999999999997</v>
       </c>
@@ -10869,7 +10869,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>28.4</v>
       </c>
@@ -10898,7 +10898,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>28.8</v>
       </c>
@@ -10927,7 +10927,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>26.8</v>
       </c>
@@ -10956,7 +10956,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>33.5</v>
       </c>
@@ -10985,7 +10985,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>41.5</v>
       </c>
@@ -11014,7 +11014,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>38.1</v>
       </c>
@@ -11043,7 +11043,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>32.1</v>
       </c>
@@ -11072,7 +11072,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>37.200000000000003</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>28</v>
       </c>
@@ -11130,7 +11130,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>26.4</v>
       </c>
@@ -11159,7 +11159,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>24.3</v>
       </c>
@@ -11188,7 +11188,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>19.100000000000001</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>34.299999999999997</v>
       </c>
@@ -11246,7 +11246,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>29.8</v>
       </c>
@@ -11275,7 +11275,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>31.3</v>
       </c>
@@ -11304,7 +11304,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>37</v>
       </c>
@@ -11333,7 +11333,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>32.200000000000003</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>46.6</v>
       </c>
@@ -11391,7 +11391,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>27.9</v>
       </c>
@@ -11420,7 +11420,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>40.799999999999997</v>
       </c>
@@ -11449,7 +11449,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>44.3</v>
       </c>
@@ -11478,7 +11478,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>43.4</v>
       </c>
@@ -11507,7 +11507,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>36.4</v>
       </c>
@@ -11536,7 +11536,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>30</v>
       </c>
@@ -11565,7 +11565,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>44.6</v>
       </c>
@@ -11594,7 +11594,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>40.9</v>
       </c>
@@ -11620,7 +11620,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A333">
         <v>33.799999999999997</v>
       </c>
@@ -11649,7 +11649,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A334">
         <v>29.8</v>
       </c>
@@ -11678,7 +11678,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A335">
         <v>32.700000000000003</v>
       </c>
@@ -11707,7 +11707,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A336">
         <v>23.7</v>
       </c>
@@ -11736,7 +11736,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A337">
         <v>35</v>
       </c>
@@ -11765,7 +11765,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A338">
         <v>23.6</v>
       </c>
@@ -11791,7 +11791,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A339">
         <v>32.4</v>
       </c>
@@ -11820,7 +11820,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A340">
         <v>27.2</v>
       </c>
@@ -11849,7 +11849,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A341">
         <v>26.6</v>
       </c>
@@ -11878,7 +11878,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A342">
         <v>25.8</v>
       </c>
@@ -11907,7 +11907,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A343">
         <v>23.5</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A344">
         <v>30</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A345">
         <v>39.1</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A346">
         <v>39</v>
       </c>
@@ -12023,7 +12023,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A347">
         <v>35.1</v>
       </c>
@@ -12052,7 +12052,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A348">
         <v>32.299999999999997</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A349">
         <v>37</v>
       </c>
@@ -12110,7 +12110,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A350">
         <v>37.700000000000003</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A351">
         <v>34.1</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A352">
         <v>34.700000000000003</v>
       </c>
@@ -12197,7 +12197,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A353">
         <v>34.4</v>
       </c>
@@ -12226,7 +12226,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A354">
         <v>29.9</v>
       </c>
@@ -12255,7 +12255,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A355">
         <v>33</v>
       </c>
@@ -12284,7 +12284,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A356">
         <v>34.5</v>
       </c>
@@ -12310,7 +12310,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A357">
         <v>33.700000000000003</v>
       </c>
@@ -12339,7 +12339,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A358">
         <v>32.4</v>
       </c>
@@ -12368,7 +12368,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A359">
         <v>32.9</v>
       </c>
@@ -12397,7 +12397,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A360">
         <v>31.6</v>
       </c>
@@ -12426,7 +12426,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A361">
         <v>28.1</v>
       </c>
@@ -12455,7 +12455,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A362">
         <v>30.7</v>
       </c>
@@ -12484,7 +12484,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A363">
         <v>25.4</v>
       </c>
@@ -12513,7 +12513,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A364">
         <v>24.2</v>
       </c>
@@ -12542,7 +12542,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A365">
         <v>22.4</v>
       </c>
@@ -12571,7 +12571,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A366">
         <v>26.6</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A367">
         <v>20.2</v>
       </c>
@@ -12629,7 +12629,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A368">
         <v>17.600000000000001</v>
       </c>
@@ -12658,7 +12658,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A369">
         <v>28</v>
       </c>
@@ -12687,7 +12687,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A370">
         <v>27</v>
       </c>
@@ -12716,7 +12716,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A371">
         <v>34</v>
       </c>
@@ -12745,7 +12745,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A372">
         <v>31</v>
       </c>
@@ -12774,7 +12774,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A373">
         <v>29</v>
       </c>
@@ -12803,7 +12803,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A374">
         <v>27</v>
       </c>
@@ -12832,7 +12832,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A375">
         <v>24</v>
       </c>
@@ -12861,7 +12861,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A376">
         <v>23</v>
       </c>
@@ -12887,7 +12887,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A377">
         <v>36</v>
       </c>
@@ -12916,7 +12916,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A378">
         <v>37</v>
       </c>
@@ -12945,7 +12945,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A379">
         <v>31</v>
       </c>
@@ -12974,7 +12974,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A380">
         <v>38</v>
       </c>
@@ -13003,7 +13003,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A381">
         <v>36</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A382">
         <v>36</v>
       </c>
@@ -13061,7 +13061,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A383">
         <v>36</v>
       </c>
@@ -13090,7 +13090,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A384">
         <v>34</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A385">
         <v>38</v>
       </c>
@@ -13148,7 +13148,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A386">
         <v>32</v>
       </c>
@@ -13177,7 +13177,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A387">
         <v>38</v>
       </c>
@@ -13206,7 +13206,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A388">
         <v>25</v>
       </c>
@@ -13235,7 +13235,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A389">
         <v>38</v>
       </c>
@@ -13264,7 +13264,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A390">
         <v>26</v>
       </c>
@@ -13293,7 +13293,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A391">
         <v>22</v>
       </c>
@@ -13322,7 +13322,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A392">
         <v>32</v>
       </c>
@@ -13351,7 +13351,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A393">
         <v>36</v>
       </c>
@@ -13380,7 +13380,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A394">
         <v>27</v>
       </c>
@@ -13409,7 +13409,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A395">
         <v>27</v>
       </c>
@@ -13438,7 +13438,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A396">
         <v>44</v>
       </c>
@@ -13467,7 +13467,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A397">
         <v>32</v>
       </c>
@@ -13496,7 +13496,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A398">
         <v>28</v>
       </c>
@@ -13525,7 +13525,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A399">
         <v>31</v>
       </c>
@@ -13566,19 +13566,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FBD565-4521-4E30-A67D-FF1FDA2E9337}">
   <dimension ref="A1:I95"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.17578125" customWidth="1"/>
-    <col min="2" max="2" width="30.3515625" customWidth="1"/>
-    <col min="3" max="3" width="11.703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.17578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.17578125" customWidth="1"/>
-    <col min="6" max="6" width="10.46875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1171875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.05859375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.19921875" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" customWidth="1"/>
+    <col min="3" max="3" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.19921875" customWidth="1"/>
+    <col min="6" max="6" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="str" cm="1">
         <f t="array" ref="A1:F10">_xlfn._xlws.PY(1,0)</f>
         <v/>
@@ -13599,7 +13599,7 @@
         <v>unique</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="str">
         <v>mpg</v>
       </c>
@@ -13619,7 +13619,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="str">
         <v>cylinders</v>
       </c>
@@ -13639,7 +13639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="str">
         <v>displacement</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="str">
         <v>horsepower</v>
       </c>
@@ -13679,7 +13679,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="str">
         <v>weight</v>
       </c>
@@ -13699,7 +13699,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="str">
         <v>acceleration</v>
       </c>
@@ -13719,7 +13719,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="str">
         <v>model_year</v>
       </c>
@@ -13739,7 +13739,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="str">
         <v>origin</v>
       </c>
@@ -13759,7 +13759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="str">
         <v>name</v>
       </c>
@@ -13779,7 +13779,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="str" cm="1">
         <f t="array" ref="A14:I19">_xlfn._xlws.PY(2,0)</f>
         <v>mpg</v>
@@ -13809,7 +13809,7 @@
         <v>name</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>18</v>
       </c>
@@ -13838,7 +13838,7 @@
         <v>chevrolet chevelle malibu</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -13867,7 +13867,7 @@
         <v>buick skylark 320</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>18</v>
       </c>
@@ -13896,7 +13896,7 @@
         <v>plymouth satellite</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -13925,7 +13925,7 @@
         <v>amc rebel sst</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -13954,19 +13954,19 @@
         <v>ford torino</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="str" cm="1">
         <f t="array" ref="A21">_xlfn._xlws.PY(3,0)</f>
         <v>Before: 398 rows, After: 392 rows, Removed: 6</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="str" cm="1">
         <f t="array" ref="A23">_xlfn._xlws.PY(4,0)</f>
         <v>Median horsepower: 93.5, Missing after fill: 0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="str" cm="1">
         <f t="array" ref="A25:C30">_xlfn._xlws.PY(5,0)</f>
         <v>name</v>
@@ -13978,7 +13978,7 @@
         <v>era</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="str">
         <v>chevrolet chevelle malibu</v>
       </c>
@@ -13989,7 +13989,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="str">
         <v>buick skylark 320</v>
       </c>
@@ -14000,7 +14000,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="str">
         <v>plymouth satellite</v>
       </c>
@@ -14011,7 +14011,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="str">
         <v>amc rebel sst</v>
       </c>
@@ -14022,7 +14022,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="str">
         <v>ford torino</v>
       </c>
@@ -14033,7 +14033,7 @@
         <v>Early 1970s</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" t="str" cm="1">
         <f t="array" ref="A33:B36">_xlfn._xlws.PY(6,0)</f>
         <v>origin</v>
@@ -14042,7 +14042,7 @@
         <v>power_to_weight</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" t="str">
         <v>europe</v>
       </c>
@@ -14050,7 +14050,7 @@
         <v>33.69</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" t="str">
         <v>japan</v>
       </c>
@@ -14058,7 +14058,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" t="str">
         <v>usa</v>
       </c>
@@ -14066,7 +14066,7 @@
         <v>34.97</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" t="str" cm="1">
         <f t="array" ref="A39:F43">_xlfn._xlws.PY(7,0)</f>
         <v>cylinders</v>
@@ -14087,7 +14087,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A40" t="str">
         <v>origin</v>
       </c>
@@ -14107,7 +14107,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" t="str">
         <v>europe</v>
       </c>
@@ -14127,7 +14127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" t="str">
         <v>japan</v>
       </c>
@@ -14147,7 +14147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" t="str">
         <v>usa</v>
       </c>
@@ -14167,7 +14167,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" t="str" cm="1">
         <f t="array" ref="A46:F50">_xlfn._xlws.PY(8,0)</f>
         <v>cylinders</v>
@@ -14188,7 +14188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A47" t="str">
         <v>origin</v>
       </c>
@@ -14208,7 +14208,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" t="str">
         <v>europe</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" t="str">
         <v>japan</v>
       </c>
@@ -14248,7 +14248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" t="str">
         <v>usa</v>
       </c>
@@ -14268,19 +14268,19 @@
         <v>0.41399999999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" t="e" cm="1" vm="2">
         <f t="array" ref="A54">_xlfn._xlws.PY(9,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A74" t="e" cm="1" vm="3">
         <f t="array" ref="A74">_xlfn._xlws.PY(10,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" t="str" cm="1">
         <f t="array" ref="A89:G92">_xlfn._xlws.PY(11,0)</f>
         <v/>
@@ -14304,7 +14304,7 @@
         <v>model_year</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>344</v>
       </c>
@@ -14327,7 +14327,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>378</v>
       </c>
@@ -14350,7 +14350,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>387</v>
       </c>
@@ -14373,7 +14373,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" t="e" cm="1" vm="4">
         <f t="array" ref="A95">_xlfn._xlws.PY(12,0)</f>
         <v>#VALUE!</v>

--- a/ch_04/ch_04_solution.xlsx
+++ b/ch_04/ch_04_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30515"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8603F6F-2B34-4614-9750-0CD8BBE86C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D767FA56-0E03-4735-B07D-F122164654AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1302,16 +1302,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1333500</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>80433</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>250092</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>690563</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>131233</xdr:rowOff>
+      <xdr:rowOff>1573269</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1339,8 +1339,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1333500" y="15553266"/>
-          <a:ext cx="3281159" cy="2235200"/>
+          <a:off x="942975" y="13291608"/>
+          <a:ext cx="5367338" cy="3664536"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1357,10 +1357,10 @@
       <xdr:rowOff>156367</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>191035</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>16932</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>122105</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1388,8 +1388,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1206499" y="17813600"/>
-          <a:ext cx="4652969" cy="3319199"/>
+          <a:off x="1196974" y="19525455"/>
+          <a:ext cx="6532564" cy="4671088"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14280,6 +14280,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="86" spans="1:7" ht="157.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" t="str" cm="1">
         <f t="array" ref="A89:G92">_xlfn._xlws.PY(11,0)</f>
